--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +736,65 @@
           <t>06-07-2026 10:32</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ20260707073238</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7620096199</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>bharteshsavale2112@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>07-07-2026 07:32</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,10 +743,8 @@
           <t>REQ20260707073238</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
+      <c r="B6" t="n">
+        <v>123456</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -758,10 +756,8 @@
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>7620096199</t>
-        </is>
+      <c r="E6" t="n">
+        <v>7620096199</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -773,11 +769,7 @@
           <t>1st Shift</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>moshi</t>
@@ -795,6 +787,67 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ20260707125744</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vvvvv@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>07-07-2026 12:57</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>07-07-2026 12:58</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -1,88 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/710036f0a3319146/Desktop/updated project/SHARED SUPPORT SERVICE APP/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3A0D14FD7DB2D1159C9E8317C31E2BC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC34DA3A-34B4-4C80-99D5-CDEDC8402261}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>requestId</t>
-  </si>
-  <si>
-    <t>employeeCode</t>
-  </si>
-  <si>
-    <t>employeeName</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>mobile</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>shift</t>
-  </si>
-  <si>
-    <t>routeNumber</t>
-  </si>
-  <si>
-    <t>busStop</t>
-  </si>
-  <si>
-    <t>requestDate</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>approvedBy</t>
-  </si>
-  <si>
-    <t>approvedDate</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -97,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,49 +420,433 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>requestId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>employeeCode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>employeeName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>routeNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>busStop</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>requestDate</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>approvedBy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>approvedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ20260703200321</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bharteshsavale2112@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>03-07-2026 20:03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ20260706071337</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7410</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sakshi</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9156396198</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sakshi@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>chakan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>06-07-2026 07:13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>06-07-2026 07:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ20260706072148</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9090</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>9921531890</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>vishal@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>06-07-2026 07:21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>06-07-2026 07:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ20260706103101</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sachin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7788639090</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sachin@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>12</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>06-07-2026 10:31</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>06-07-2026 10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ20260707073238</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>bharteshsavale2112@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>07-07-2026 07:32</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ20260707125744</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vvvvv@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>07-07-2026 12:57</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>07-07-2026 12:58</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2E7ACE-82A0-46FB-9857-EA5CA0948741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13135,27 +13135,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{8AEB35C8-14DC-4564-9EF2-60BFDF011EBD}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -72485,7 +72465,7 @@
         <v>9938097309</v>
       </c>
       <c r="E1412" s="3" t="s">
-        <v>3001</v>
+        <v>3108</v>
       </c>
       <c r="F1412" s="5" t="str">
         <f t="shared" si="22"/>
@@ -72495,10 +72475,10 @@
         <v>17</v>
       </c>
       <c r="H1412" s="4" t="s">
-        <v>1962</v>
+        <v>2093</v>
       </c>
       <c r="I1412" s="6">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J1412" s="18">
         <v>46217</v>
@@ -72507,7 +72487,7 @@
         <v>229085</v>
       </c>
       <c r="L1412" s="4" t="s">
-        <v>666</v>
+        <v>276</v>
       </c>
       <c r="M1412" s="18">
         <v>46217</v>
@@ -90539,13 +90519,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1825:A1831">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1825:A1851">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C1824">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D23B5A2-9EC3-4167-ACAE-8A3FB0FDB427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10914" uniqueCount="4318">
   <si>
     <t>requestId</t>
   </si>
@@ -88914,15 +88914,21 @@
       <c r="G1808" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1808" s="4"/>
-      <c r="I1808" s="6"/>
+      <c r="H1808" s="4" t="s">
+        <v>1886</v>
+      </c>
+      <c r="I1808" s="6">
+        <v>33</v>
+      </c>
       <c r="J1808" s="18">
         <v>46217</v>
       </c>
       <c r="K1808" s="8">
         <v>232678</v>
       </c>
-      <c r="L1808" s="4"/>
+      <c r="L1808" s="4" t="s">
+        <v>1910</v>
+      </c>
       <c r="M1808" s="18">
         <v>46217</v>
       </c>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D23B5A2-9EC3-4167-ACAE-8A3FB0FDB427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10914" uniqueCount="4318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
   <si>
     <t>requestId</t>
   </si>
@@ -88914,21 +88914,15 @@
       <c r="G1808" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1808" s="4" t="s">
-        <v>1886</v>
-      </c>
-      <c r="I1808" s="6">
-        <v>33</v>
-      </c>
+      <c r="H1808" s="4"/>
+      <c r="I1808" s="6"/>
       <c r="J1808" s="18">
         <v>46217</v>
       </c>
       <c r="K1808" s="8">
         <v>232678</v>
       </c>
-      <c r="L1808" s="4" t="s">
-        <v>1910</v>
-      </c>
+      <c r="L1808" s="4"/>
       <c r="M1808" s="18">
         <v>46217</v>
       </c>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B5B7-86E1-487C-AF19-A43B35E55C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10913" uniqueCount="4319">
   <si>
     <t>requestId</t>
   </si>
@@ -12985,6 +12985,9 @@
   </si>
   <si>
     <t>REQ20260715155000</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -13464,7 +13467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1852"/>
+  <dimension ref="A1:O1852"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -47683,7 +47686,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="817" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2016</v>
       </c>
@@ -47707,10 +47710,10 @@
         <v>17</v>
       </c>
       <c r="H817" s="4" t="s">
-        <v>1436</v>
+        <v>409</v>
       </c>
       <c r="I817" s="6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J817" s="18">
         <v>46217</v>
@@ -47719,13 +47722,13 @@
         <v>129902</v>
       </c>
       <c r="L817" s="4" t="s">
-        <v>272</v>
+        <v>2083</v>
       </c>
       <c r="M817" s="18">
         <v>46217</v>
       </c>
     </row>
-    <row r="818" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2018</v>
       </c>
@@ -47767,7 +47770,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="819" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2020</v>
       </c>
@@ -47809,7 +47812,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="820" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2022</v>
       </c>
@@ -47851,7 +47854,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="821" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2025</v>
       </c>
@@ -47892,8 +47895,11 @@
       <c r="M821" s="18">
         <v>46217</v>
       </c>
-    </row>
-    <row r="822" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O821" t="s">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="822" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2027</v>
       </c>
@@ -47935,7 +47941,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="823" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2029</v>
       </c>
@@ -47977,7 +47983,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="824" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2031</v>
       </c>
@@ -48019,7 +48025,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="825" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2033</v>
       </c>
@@ -48061,7 +48067,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="826" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2035</v>
       </c>
@@ -48103,7 +48109,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="827" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2037</v>
       </c>
@@ -48145,7 +48151,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="828" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2039</v>
       </c>
@@ -48187,7 +48193,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="829" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2041</v>
       </c>
@@ -48229,7 +48235,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="830" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2045</v>
       </c>
@@ -48271,7 +48277,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="831" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2048</v>
       </c>
@@ -48313,7 +48319,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="832" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2051</v>
       </c>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B5B7-86E1-487C-AF19-A43B35E55C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10913" uniqueCount="4319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
   <si>
     <t>requestId</t>
   </si>
@@ -12985,9 +12985,6 @@
   </si>
   <si>
     <t>REQ20260715155000</t>
-  </si>
-  <si>
-    <t>F</t>
   </si>
 </sst>
 </file>
@@ -13467,7 +13464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1852"/>
+  <dimension ref="A1:M1852"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -47686,7 +47683,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2016</v>
       </c>
@@ -47710,10 +47707,10 @@
         <v>17</v>
       </c>
       <c r="H817" s="4" t="s">
-        <v>409</v>
+        <v>1436</v>
       </c>
       <c r="I817" s="6">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J817" s="18">
         <v>46217</v>
@@ -47722,13 +47719,13 @@
         <v>129902</v>
       </c>
       <c r="L817" s="4" t="s">
-        <v>2083</v>
+        <v>272</v>
       </c>
       <c r="M817" s="18">
         <v>46217</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2018</v>
       </c>
@@ -47770,7 +47767,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="819" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2020</v>
       </c>
@@ -47812,7 +47809,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="820" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2022</v>
       </c>
@@ -47854,7 +47851,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="821" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2025</v>
       </c>
@@ -47895,11 +47892,8 @@
       <c r="M821" s="18">
         <v>46217</v>
       </c>
-      <c r="O821" t="s">
-        <v>4318</v>
-      </c>
-    </row>
-    <row r="822" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="822" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2027</v>
       </c>
@@ -47941,7 +47935,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2029</v>
       </c>
@@ -47983,7 +47977,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2031</v>
       </c>
@@ -48025,7 +48019,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="825" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2033</v>
       </c>
@@ -48067,7 +48061,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2035</v>
       </c>
@@ -48109,7 +48103,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2037</v>
       </c>
@@ -48151,7 +48145,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2039</v>
       </c>
@@ -48193,7 +48187,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2041</v>
       </c>
@@ -48235,7 +48229,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2045</v>
       </c>
@@ -48277,7 +48271,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="831" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2048</v>
       </c>
@@ -48319,7 +48313,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="832" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2051</v>
       </c>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B5B7-86E1-487C-AF19-A43B35E55C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0958F58-4E34-4BC1-9C9A-494B776A3A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73026,11 +73026,11 @@
       <c r="G1425" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1425" s="4" t="s">
-        <v>1910</v>
+      <c r="H1425" t="s">
+        <v>250</v>
       </c>
       <c r="I1425" s="6">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J1425" s="18">
         <v>46217</v>
@@ -73038,8 +73038,8 @@
       <c r="K1425" s="2">
         <v>229223</v>
       </c>
-      <c r="L1425" s="4" t="s">
-        <v>1910</v>
+      <c r="L1425" t="s">
+        <v>66</v>
       </c>
       <c r="M1425" s="18">
         <v>46217</v>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0958F58-4E34-4BC1-9C9A-494B776A3A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10913" uniqueCount="4319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
   <si>
     <t>requestId</t>
   </si>
@@ -12985,9 +12985,6 @@
   </si>
   <si>
     <t>REQ20260715155000</t>
-  </si>
-  <si>
-    <t>F</t>
   </si>
 </sst>
 </file>
@@ -13467,7 +13464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1852"/>
+  <dimension ref="A1:M1852"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -47686,7 +47683,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2016</v>
       </c>
@@ -47710,10 +47707,10 @@
         <v>17</v>
       </c>
       <c r="H817" s="4" t="s">
-        <v>409</v>
+        <v>1436</v>
       </c>
       <c r="I817" s="6">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J817" s="18">
         <v>46217</v>
@@ -47722,13 +47719,13 @@
         <v>129902</v>
       </c>
       <c r="L817" s="4" t="s">
-        <v>2083</v>
+        <v>272</v>
       </c>
       <c r="M817" s="18">
         <v>46217</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2018</v>
       </c>
@@ -47770,7 +47767,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="819" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2020</v>
       </c>
@@ -47812,7 +47809,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="820" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2022</v>
       </c>
@@ -47854,7 +47851,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="821" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2025</v>
       </c>
@@ -47895,11 +47892,8 @@
       <c r="M821" s="18">
         <v>46217</v>
       </c>
-      <c r="O821" t="s">
-        <v>4318</v>
-      </c>
-    </row>
-    <row r="822" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="822" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2027</v>
       </c>
@@ -47941,7 +47935,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2029</v>
       </c>
@@ -47983,7 +47977,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2031</v>
       </c>
@@ -48025,7 +48019,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="825" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2033</v>
       </c>
@@ -48067,7 +48061,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2035</v>
       </c>
@@ -48109,7 +48103,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2037</v>
       </c>
@@ -48151,7 +48145,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2039</v>
       </c>
@@ -48193,7 +48187,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2041</v>
       </c>
@@ -48235,7 +48229,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2045</v>
       </c>
@@ -48277,7 +48271,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="831" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2048</v>
       </c>
@@ -48319,7 +48313,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="832" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2051</v>
       </c>
@@ -73026,11 +73020,11 @@
       <c r="G1425" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1425" t="s">
-        <v>250</v>
+      <c r="H1425" s="4" t="s">
+        <v>1910</v>
       </c>
       <c r="I1425" s="6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J1425" s="18">
         <v>46217</v>
@@ -73038,8 +73032,8 @@
       <c r="K1425" s="2">
         <v>229223</v>
       </c>
-      <c r="L1425" t="s">
-        <v>66</v>
+      <c r="L1425" s="4" t="s">
+        <v>1910</v>
       </c>
       <c r="M1425" s="18">
         <v>46217</v>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C95D2-E510-467C-867A-2A1DF3F9EE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52486D11-6F7D-45FB-92E8-41C793EB171E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10912" uniqueCount="4318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10914" uniqueCount="4319">
   <si>
     <t>requestId</t>
   </si>
@@ -12985,6 +12985,9 @@
   </si>
   <si>
     <t>REQ20260715155000</t>
+  </si>
+  <si>
+    <t>MALINAGAR</t>
   </si>
 </sst>
 </file>
@@ -47707,10 +47710,10 @@
         <v>17</v>
       </c>
       <c r="H817" s="4" t="s">
-        <v>1436</v>
+        <v>2213</v>
       </c>
       <c r="I817" s="6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J817" s="18">
         <v>46217</v>
@@ -47719,7 +47722,7 @@
         <v>129902</v>
       </c>
       <c r="L817" s="4" t="s">
-        <v>272</v>
+        <v>409</v>
       </c>
       <c r="M817" s="18">
         <v>46217</v>
@@ -88554,15 +88557,21 @@
       <c r="G1798" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1798" s="4"/>
-      <c r="I1798" s="6"/>
+      <c r="H1798" s="4" t="s">
+        <v>4318</v>
+      </c>
+      <c r="I1798" s="6">
+        <v>29</v>
+      </c>
       <c r="J1798" s="18">
         <v>46217</v>
       </c>
       <c r="K1798" s="8">
         <v>232668</v>
       </c>
-      <c r="L1798" s="4"/>
+      <c r="L1798" s="4" t="s">
+        <v>3897</v>
+      </c>
       <c r="M1798" s="18">
         <v>46217</v>
       </c>

--- a/pass_requests.xlsx
+++ b/pass_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B5B7-86E1-487C-AF19-A43B35E55C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF59CB-F5F5-444E-B871-65D5690C509D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76135,10 +76135,10 @@
         <v>17</v>
       </c>
       <c r="H1500" s="4" t="s">
-        <v>1962</v>
+        <v>2060</v>
       </c>
       <c r="I1500" s="6">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J1500" s="18">
         <v>46217</v>
@@ -76147,7 +76147,7 @@
         <v>230227</v>
       </c>
       <c r="L1500" s="4" t="s">
-        <v>666</v>
+        <v>143</v>
       </c>
       <c r="M1500" s="18">
         <v>46217</v>
